--- a/review-results/复盘信息抓取-20260901.xlsx
+++ b/review-results/复盘信息抓取-20260901.xlsx
@@ -5113,8 +5113,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>12936.853</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>411.135</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5138,8 +5157,27 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>13100.304</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>413.138</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5163,8 +5201,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>13393.454</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>400.008</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5188,8 +5245,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>13061.654</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>404.07</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5213,8 +5289,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>12702.451</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>399.945</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5238,8 +5333,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>13340.761</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>399.558</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5263,8 +5377,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>15281.894</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>418.558</v>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5288,8 +5421,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>16387.686</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>412.59</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5313,8 +5465,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>15156.966</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>271.84</v>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5338,8 +5509,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>15351.418</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5363,8 +5553,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>16233.877</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5388,8 +5597,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>17354.252</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>174.893</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5413,8 +5641,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>17656.215</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>176.833</v>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5438,8 +5685,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>16486.963</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>86.7</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5463,8 +5729,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>15786.823</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>137.523</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5488,8 +5773,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>16304.584</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>361.195</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5513,8 +5817,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>15761.019</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>381.925</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5538,8 +5861,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>16373.426</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>382.325</v>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5563,8 +5905,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>16024.109</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>410.995</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5588,8 +5949,27 @@
       </c>
     </row>
     <row r="21">
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>15405.345</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>421.013</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5613,8 +5993,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>13761.093</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>407.165</v>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5638,8 +6037,27 @@
       </c>
     </row>
     <row r="23">
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>13110.744</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>397.448</v>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5663,8 +6081,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>13578.02</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>399.955</v>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5688,8 +6125,27 @@
       </c>
     </row>
     <row r="25">
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>13574.047</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>397.31</v>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -15174,9 +15630,7 @@
       <c r="C2" s="3" t="n">
         <v>28733.9</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>8469.790000000001</v>
-      </c>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
@@ -15201,9 +15655,7 @@
       <c r="C3" s="3" t="n">
         <v>28657.3</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>8460.120000000001</v>
-      </c>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
@@ -15228,9 +15680,7 @@
       <c r="C4" s="3" t="n">
         <v>28454.4</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>8449.43</v>
-      </c>
+      <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
@@ -15255,9 +15705,7 @@
       <c r="C5" s="3" t="n">
         <v>28386</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>8440.84</v>
-      </c>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
@@ -15282,9 +15730,7 @@
       <c r="C6" s="3" t="n">
         <v>29340.5</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>8426.799999999999</v>
-      </c>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
@@ -15309,9 +15755,7 @@
       <c r="C7" s="3" t="n">
         <v>29041.5</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>8419.35</v>
-      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
@@ -15336,9 +15780,7 @@
       <c r="C8" s="3" t="n">
         <v>28975.6</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>8413.73</v>
-      </c>
+      <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
@@ -15363,9 +15805,7 @@
       <c r="C9" s="3" t="n">
         <v>28575.7</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>8406.17</v>
-      </c>
+      <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
@@ -15390,9 +15830,7 @@
       <c r="C10" s="3" t="n">
         <v>30675.2</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>8398.01</v>
-      </c>
+      <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15855,7 @@
       <c r="C11" s="3" t="n">
         <v>30603.5</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>8391.42</v>
-      </c>
+      <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
@@ -15444,9 +15880,7 @@
       <c r="C12" s="3" t="n">
         <v>29623.7</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>8385.280000000001</v>
-      </c>
+      <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
@@ -15471,9 +15905,7 @@
       <c r="C13" s="3" t="n">
         <v>29597.5</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>8378.5</v>
-      </c>
+      <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
@@ -15498,9 +15930,7 @@
       <c r="C14" s="3" t="n">
         <v>28805.1</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>8375.540000000001</v>
-      </c>
+      <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
@@ -15525,9 +15955,7 @@
       <c r="C15" s="3" t="n">
         <v>28541</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>8369.610000000001</v>
-      </c>
+      <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
@@ -15552,9 +15980,7 @@
       <c r="C16" s="3" t="n">
         <v>28403.3</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>8364.540000000001</v>
-      </c>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
@@ -15579,9 +16005,7 @@
       <c r="C17" s="3" t="n">
         <v>27788.1</v>
       </c>
-      <c r="D17" s="3" t="n">
-        <v>8359.049999999999</v>
-      </c>
+      <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
@@ -15606,9 +16030,7 @@
       <c r="C18" s="3" t="n">
         <v>28123.9</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>8365.549999999999</v>
-      </c>
+      <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
@@ -15633,9 +16055,7 @@
       <c r="C19" s="3" t="n">
         <v>27779.9</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>8363.299999999999</v>
-      </c>
+      <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
@@ -15660,9 +16080,7 @@
       <c r="C20" s="3" t="n">
         <v>27846.3</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>8361.969999999999</v>
-      </c>
+      <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
@@ -15687,9 +16105,7 @@
       <c r="C21" s="3" t="n">
         <v>27881.6</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>8357.209999999999</v>
-      </c>
+      <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
@@ -15714,9 +16130,7 @@
       <c r="C22" s="3" t="n">
         <v>28190.5</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>8357.01</v>
-      </c>
+      <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
@@ -15741,9 +16155,7 @@
       <c r="C23" s="3" t="n">
         <v>28339.2</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>8358.02</v>
-      </c>
+      <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
@@ -15768,9 +16180,7 @@
       <c r="C24" s="3" t="n">
         <v>28465.3</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>8365.299999999999</v>
-      </c>
+      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n">
         <v>7</v>
       </c>
@@ -15795,9 +16205,7 @@
       <c r="C25" s="3" t="n">
         <v>28793.8</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>8367.16</v>
-      </c>
+      <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n">
         <v>89.09999999999999</v>
       </c>
@@ -15822,9 +16230,7 @@
       <c r="C26" s="3" t="n">
         <v>29071.7</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>8143.12</v>
-      </c>
+      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n">
         <v>356.4</v>
       </c>
@@ -15849,9 +16255,7 @@
       <c r="C27" s="3" t="n">
         <v>29252.3</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>7709.08</v>
-      </c>
+      <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n">
         <v>759.1</v>
       </c>
@@ -15876,9 +16280,7 @@
       <c r="C28" s="3" t="n">
         <v>28805.5</v>
       </c>
-      <c r="D28" s="3" t="n">
-        <v>7025.75</v>
-      </c>
+      <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n">
         <v>1325.4</v>
       </c>
@@ -15903,9 +16305,7 @@
       <c r="C29" s="3" t="n">
         <v>27816.2</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>6351.08</v>
-      </c>
+      <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n">
         <v>2017.2</v>
       </c>
@@ -15930,9 +16330,7 @@
       <c r="C30" s="3" t="n">
         <v>27817.5</v>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>5887.63</v>
-      </c>
+      <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n">
         <v>2801.2</v>
       </c>
@@ -15957,9 +16355,7 @@
       <c r="C31" s="3" t="n">
         <v>26936.8</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>5406.66</v>
-      </c>
+      <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n">
         <v>3694.8</v>
       </c>
@@ -15984,9 +16380,7 @@
       <c r="C32" s="3" t="n">
         <v>26372.2</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>4946.22</v>
-      </c>
+      <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n">
         <v>4574.6</v>
       </c>
@@ -16011,9 +16405,7 @@
       <c r="C33" s="3" t="n">
         <v>26151.5</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>4531.53</v>
-      </c>
+      <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n">
         <v>5624.1</v>
       </c>
@@ -16038,9 +16430,7 @@
       <c r="C34" s="3" t="n">
         <v>26160.2</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>4184.9</v>
-      </c>
+      <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n">
         <v>6601.1</v>
       </c>
@@ -16065,9 +16455,7 @@
       <c r="C35" s="3" t="n">
         <v>26242.9</v>
       </c>
-      <c r="D35" s="3" t="n">
-        <v>4131.34</v>
-      </c>
+      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n">
         <v>7442.1</v>
       </c>
@@ -16092,9 +16480,7 @@
       <c r="C36" s="3" t="n">
         <v>25697.8</v>
       </c>
-      <c r="D36" s="3" t="n">
-        <v>4165.76</v>
-      </c>
+      <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n">
         <v>8148.2</v>
       </c>
@@ -16119,9 +16505,7 @@
       <c r="C37" s="3" t="n">
         <v>25462.6</v>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>4177.73</v>
-      </c>
+      <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n">
         <v>8710.5</v>
       </c>
@@ -16146,9 +16530,7 @@
       <c r="C38" s="3" t="n">
         <v>25112.7</v>
       </c>
-      <c r="D38" s="3" t="n">
-        <v>4202.95</v>
-      </c>
+      <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n">
         <v>9337.700000000001</v>
       </c>
@@ -16173,9 +16555,7 @@
       <c r="C39" s="3" t="n">
         <v>24681.6</v>
       </c>
-      <c r="D39" s="3" t="n">
-        <v>4234.98</v>
-      </c>
+      <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n">
         <v>9769.299999999999</v>
       </c>
@@ -16200,9 +16580,7 @@
       <c r="C40" s="3" t="n">
         <v>24691.5</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>4276.17</v>
-      </c>
+      <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="n">
         <v>9695.799999999999</v>
       </c>
@@ -16227,9 +16605,7 @@
       <c r="C41" s="3" t="n">
         <v>24250</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>4290.27</v>
-      </c>
+      <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="n">
         <v>9266.9</v>
       </c>
@@ -16254,9 +16630,7 @@
       <c r="C42" s="3" t="n">
         <v>24420.1</v>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>4314.45</v>
-      </c>
+      <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="n">
         <v>9417.1</v>
       </c>
@@ -16281,9 +16655,7 @@
       <c r="C43" s="3" t="n">
         <v>24473.7</v>
       </c>
-      <c r="D43" s="3" t="n">
-        <v>4331.38</v>
-      </c>
+      <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n">
         <v>9414.799999999999</v>
       </c>
@@ -16308,9 +16680,7 @@
       <c r="C44" s="3" t="n">
         <v>24508.9</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>4357.8</v>
-      </c>
+      <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n">
         <v>9667.200000000001</v>
       </c>
@@ -16335,9 +16705,7 @@
       <c r="C45" s="3" t="n">
         <v>24564</v>
       </c>
-      <c r="D45" s="3" t="n">
-        <v>4366.63</v>
-      </c>
+      <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n">
         <v>9996.799999999999</v>
       </c>
@@ -16362,9 +16730,7 @@
       <c r="C46" s="3" t="n">
         <v>26246.1</v>
       </c>
-      <c r="D46" s="3" t="n">
-        <v>4395.82</v>
-      </c>
+      <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="n">
         <v>11289</v>
       </c>
@@ -16389,9 +16755,7 @@
       <c r="C47" s="3" t="n">
         <v>26175.9</v>
       </c>
-      <c r="D47" s="3" t="n">
-        <v>4415.28</v>
-      </c>
+      <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="n">
         <v>11699</v>
       </c>
@@ -16416,9 +16780,7 @@
       <c r="C48" s="3" t="n">
         <v>25690</v>
       </c>
-      <c r="D48" s="3" t="n">
-        <v>4412.62</v>
-      </c>
+      <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n">
         <v>11537.9</v>
       </c>
@@ -16443,9 +16805,7 @@
       <c r="C49" s="3" t="n">
         <v>24471.3</v>
       </c>
-      <c r="D49" s="3" t="n">
-        <v>4366.12</v>
-      </c>
+      <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n">
         <v>11331.1</v>
       </c>
@@ -16470,9 +16830,7 @@
       <c r="C50" s="3" t="n">
         <v>24840.2</v>
       </c>
-      <c r="D50" s="3" t="n">
-        <v>4371.46</v>
-      </c>
+      <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n">
         <v>11673.4</v>
       </c>
@@ -16497,9 +16855,7 @@
       <c r="C51" s="3" t="n">
         <v>24879.7</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>4352.78</v>
-      </c>
+      <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="n">
         <v>11656.4</v>
       </c>
@@ -16524,9 +16880,7 @@
       <c r="C52" s="3" t="n">
         <v>24570.9</v>
       </c>
-      <c r="D52" s="3" t="n">
-        <v>4368.49</v>
-      </c>
+      <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="n">
         <v>11529.7</v>
       </c>
@@ -16551,9 +16905,7 @@
       <c r="C53" s="3" t="n">
         <v>24892.6</v>
       </c>
-      <c r="D53" s="3" t="n">
-        <v>4367.9</v>
-      </c>
+      <c r="D53" s="3" t="n"/>
       <c r="E53" s="3" t="n">
         <v>11555.1</v>
       </c>
@@ -16578,9 +16930,7 @@
       <c r="C54" s="3" t="n">
         <v>25109.4</v>
       </c>
-      <c r="D54" s="3" t="n">
-        <v>4358.7</v>
-      </c>
+      <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="n">
         <v>11394.5</v>
       </c>
@@ -16605,9 +16955,7 @@
       <c r="C55" s="3" t="n">
         <v>25250.3</v>
       </c>
-      <c r="D55" s="3" t="n">
-        <v>4359.53</v>
-      </c>
+      <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="n">
         <v>11434.4</v>
       </c>
@@ -16632,9 +16980,7 @@
       <c r="C56" s="3" t="n">
         <v>25482.2</v>
       </c>
-      <c r="D56" s="3" t="n">
-        <v>4355.94</v>
-      </c>
+      <c r="D56" s="3" t="n"/>
       <c r="E56" s="3" t="n">
         <v>11208.7</v>
       </c>
@@ -16659,9 +17005,7 @@
       <c r="C57" s="3" t="n">
         <v>25398.3</v>
       </c>
-      <c r="D57" s="3" t="n">
-        <v>4347.6</v>
-      </c>
+      <c r="D57" s="3" t="n"/>
       <c r="E57" s="3" t="n">
         <v>10812</v>
       </c>
@@ -16686,9 +17030,7 @@
       <c r="C58" s="3" t="n">
         <v>26034.9</v>
       </c>
-      <c r="D58" s="3" t="n">
-        <v>4334.79</v>
-      </c>
+      <c r="D58" s="3" t="n"/>
       <c r="E58" s="3" t="n">
         <v>10482.5</v>
       </c>
@@ -16713,9 +17055,7 @@
       <c r="C59" s="3" t="n">
         <v>26256.7</v>
       </c>
-      <c r="D59" s="3" t="n">
-        <v>4351.18</v>
-      </c>
+      <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n">
         <v>9945.200000000001</v>
       </c>
@@ -16740,9 +17080,7 @@
       <c r="C60" s="3" t="n">
         <v>26676.4</v>
       </c>
-      <c r="D60" s="3" t="n">
-        <v>4345.68</v>
-      </c>
+      <c r="D60" s="3" t="n"/>
       <c r="E60" s="3" t="n">
         <v>9774.700000000001</v>
       </c>
@@ -16767,9 +17105,7 @@
       <c r="C61" s="3" t="n">
         <v>26870.1</v>
       </c>
-      <c r="D61" s="3" t="n">
-        <v>4322.28</v>
-      </c>
+      <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="n">
         <v>9439.700000000001</v>
       </c>
@@ -16794,9 +17130,7 @@
       <c r="C62" s="3" t="n">
         <v>27201.4</v>
       </c>
-      <c r="D62" s="3" t="n">
-        <v>4401.33</v>
-      </c>
+      <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="n">
         <v>8903.5</v>
       </c>
@@ -16821,9 +17155,7 @@
       <c r="C63" s="3" t="n">
         <v>28113.2</v>
       </c>
-      <c r="D63" s="3" t="n">
-        <v>4782.72</v>
-      </c>
+      <c r="D63" s="3" t="n"/>
       <c r="E63" s="3" t="n">
         <v>8444.299999999999</v>
       </c>
@@ -16848,9 +17180,7 @@
       <c r="C64" s="3" t="n">
         <v>28504.6</v>
       </c>
-      <c r="D64" s="3" t="n">
-        <v>5207.14</v>
-      </c>
+      <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="n">
         <v>7969.9</v>
       </c>
@@ -16875,9 +17205,7 @@
       <c r="C65" s="3" t="n">
         <v>28968.9</v>
       </c>
-      <c r="D65" s="3" t="n">
-        <v>5878.63</v>
-      </c>
+      <c r="D65" s="3" t="n"/>
       <c r="E65" s="3" t="n">
         <v>7210.5</v>
       </c>
@@ -16902,9 +17230,7 @@
       <c r="C66" s="3" t="n">
         <v>29785.8</v>
       </c>
-      <c r="D66" s="3" t="n">
-        <v>6546.52</v>
-      </c>
+      <c r="D66" s="3" t="n"/>
       <c r="E66" s="3" t="n">
         <v>6478.7</v>
       </c>
@@ -16929,9 +17255,7 @@
       <c r="C67" s="3" t="n">
         <v>30720.8</v>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>7010.45</v>
-      </c>
+      <c r="D67" s="3" t="n"/>
       <c r="E67" s="3" t="n">
         <v>5780.7</v>
       </c>
@@ -16956,9 +17280,7 @@
       <c r="C68" s="3" t="n">
         <v>31812.4</v>
       </c>
-      <c r="D68" s="3" t="n">
-        <v>7476.59</v>
-      </c>
+      <c r="D68" s="3" t="n"/>
       <c r="E68" s="3" t="n">
         <v>4917.5</v>
       </c>
@@ -16983,9 +17305,7 @@
       <c r="C69" s="3" t="n">
         <v>33027.1</v>
       </c>
-      <c r="D69" s="3" t="n">
-        <v>7938.2</v>
-      </c>
+      <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="n">
         <v>4066.9</v>
       </c>
@@ -17010,9 +17330,7 @@
       <c r="C70" s="3" t="n">
         <v>34254.8</v>
       </c>
-      <c r="D70" s="3" t="n">
-        <v>8352.440000000001</v>
-      </c>
+      <c r="D70" s="3" t="n"/>
       <c r="E70" s="3" t="n">
         <v>3167.9</v>
       </c>
@@ -17037,9 +17355,7 @@
       <c r="C71" s="3" t="n">
         <v>34931.5</v>
       </c>
-      <c r="D71" s="3" t="n">
-        <v>8562.01</v>
-      </c>
+      <c r="D71" s="3" t="n"/>
       <c r="E71" s="3" t="n">
         <v>2286.4</v>
       </c>
@@ -17064,9 +17380,7 @@
       <c r="C72" s="3" t="n">
         <v>35486.6</v>
       </c>
-      <c r="D72" s="3" t="n">
-        <v>8529.58</v>
-      </c>
+      <c r="D72" s="3" t="n"/>
       <c r="E72" s="3" t="n">
         <v>1530.6</v>
       </c>
@@ -17091,9 +17405,7 @@
       <c r="C73" s="3" t="n">
         <v>36088.2</v>
       </c>
-      <c r="D73" s="3" t="n">
-        <v>8502.059999999999</v>
-      </c>
+      <c r="D73" s="3" t="n"/>
       <c r="E73" s="3" t="n">
         <v>934.5</v>
       </c>
@@ -17118,9 +17430,7 @@
       <c r="C74" s="3" t="n">
         <v>35760.2</v>
       </c>
-      <c r="D74" s="3" t="n">
-        <v>8486.290000000001</v>
-      </c>
+      <c r="D74" s="3" t="n"/>
       <c r="E74" s="3" t="n">
         <v>497.2</v>
       </c>
@@ -17145,9 +17455,7 @@
       <c r="C75" s="3" t="n">
         <v>36061.8</v>
       </c>
-      <c r="D75" s="3" t="n">
-        <v>8473.309999999999</v>
-      </c>
+      <c r="D75" s="3" t="n"/>
       <c r="E75" s="3" t="n">
         <v>190.4</v>
       </c>
@@ -17172,9 +17480,7 @@
       <c r="C76" s="3" t="n">
         <v>36125.6</v>
       </c>
-      <c r="D76" s="3" t="n">
-        <v>8470.440000000001</v>
-      </c>
+      <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -17199,9 +17505,7 @@
       <c r="C77" s="3" t="n">
         <v>36064.3</v>
       </c>
-      <c r="D77" s="3" t="n">
-        <v>8466.120000000001</v>
-      </c>
+      <c r="D77" s="3" t="n"/>
       <c r="E77" s="3" t="n">
         <v>0</v>
       </c>
@@ -17226,9 +17530,7 @@
       <c r="C78" s="3" t="n">
         <v>36030.9</v>
       </c>
-      <c r="D78" s="3" t="n">
-        <v>8467.18</v>
-      </c>
+      <c r="D78" s="3" t="n"/>
       <c r="E78" s="3" t="n">
         <v>0</v>
       </c>
@@ -17253,9 +17555,7 @@
       <c r="C79" s="3" t="n">
         <v>35727.2</v>
       </c>
-      <c r="D79" s="3" t="n">
-        <v>8475.75</v>
-      </c>
+      <c r="D79" s="3" t="n"/>
       <c r="E79" s="3" t="n">
         <v>0</v>
       </c>
@@ -17280,9 +17580,7 @@
       <c r="C80" s="3" t="n">
         <v>35227.6</v>
       </c>
-      <c r="D80" s="3" t="n">
-        <v>8484.969999999999</v>
-      </c>
+      <c r="D80" s="3" t="n"/>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
@@ -17307,9 +17605,7 @@
       <c r="C81" s="3" t="n">
         <v>34536.7</v>
       </c>
-      <c r="D81" s="3" t="n">
-        <v>8492.42</v>
-      </c>
+      <c r="D81" s="3" t="n"/>
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
@@ -17334,9 +17630,7 @@
       <c r="C82" s="3" t="n">
         <v>34543.9</v>
       </c>
-      <c r="D82" s="3" t="n">
-        <v>8494.379999999999</v>
-      </c>
+      <c r="D82" s="3" t="n"/>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
@@ -17361,9 +17655,7 @@
       <c r="C83" s="3" t="n">
         <v>34088.9</v>
       </c>
-      <c r="D83" s="3" t="n">
-        <v>8496.360000000001</v>
-      </c>
+      <c r="D83" s="3" t="n"/>
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
@@ -17388,9 +17680,7 @@
       <c r="C84" s="3" t="n">
         <v>33923.7</v>
       </c>
-      <c r="D84" s="3" t="n">
-        <v>8495.709999999999</v>
-      </c>
+      <c r="D84" s="3" t="n"/>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
@@ -17415,9 +17705,7 @@
       <c r="C85" s="3" t="n">
         <v>33451.3</v>
       </c>
-      <c r="D85" s="3" t="n">
-        <v>8496.389999999999</v>
-      </c>
+      <c r="D85" s="3" t="n"/>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
@@ -17442,9 +17730,7 @@
       <c r="C86" s="3" t="n">
         <v>33342.4</v>
       </c>
-      <c r="D86" s="3" t="n">
-        <v>8477.68</v>
-      </c>
+      <c r="D86" s="3" t="n"/>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
@@ -17469,9 +17755,7 @@
       <c r="C87" s="3" t="n">
         <v>32902.6</v>
       </c>
-      <c r="D87" s="3" t="n">
-        <v>8474.290000000001</v>
-      </c>
+      <c r="D87" s="3" t="n"/>
       <c r="E87" s="3" t="n">
         <v>0</v>
       </c>
@@ -17496,9 +17780,7 @@
       <c r="C88" s="3" t="n">
         <v>32520</v>
       </c>
-      <c r="D88" s="3" t="n">
-        <v>8471.379999999999</v>
-      </c>
+      <c r="D88" s="3" t="n"/>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
@@ -17523,9 +17805,7 @@
       <c r="C89" s="3" t="n">
         <v>32117.7</v>
       </c>
-      <c r="D89" s="3" t="n">
-        <v>8469.459999999999</v>
-      </c>
+      <c r="D89" s="3" t="n"/>
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
@@ -17550,9 +17830,7 @@
       <c r="C90" s="3" t="n">
         <v>31796.7</v>
       </c>
-      <c r="D90" s="3" t="n">
-        <v>8414.59</v>
-      </c>
+      <c r="D90" s="3" t="n"/>
       <c r="E90" s="3" t="n">
         <v>0</v>
       </c>
@@ -17577,9 +17855,7 @@
       <c r="C91" s="3" t="n">
         <v>31317.1</v>
       </c>
-      <c r="D91" s="3" t="n">
-        <v>8405.870000000001</v>
-      </c>
+      <c r="D91" s="3" t="n"/>
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
@@ -17604,9 +17880,7 @@
       <c r="C92" s="3" t="n">
         <v>30612.5</v>
       </c>
-      <c r="D92" s="3" t="n">
-        <v>8400.52</v>
-      </c>
+      <c r="D92" s="3" t="n"/>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
@@ -17631,9 +17905,7 @@
       <c r="C93" s="3" t="n">
         <v>30284.8</v>
       </c>
-      <c r="D93" s="3" t="n">
-        <v>8393.719999999999</v>
-      </c>
+      <c r="D93" s="3" t="n"/>
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
@@ -17658,9 +17930,7 @@
       <c r="C94" s="3" t="n">
         <v>29722.3</v>
       </c>
-      <c r="D94" s="3" t="n">
-        <v>8386.32</v>
-      </c>
+      <c r="D94" s="3" t="n"/>
       <c r="E94" s="3" t="n">
         <v>0</v>
       </c>
@@ -17685,9 +17955,7 @@
       <c r="C95" s="3" t="n">
         <v>29172.8</v>
       </c>
-      <c r="D95" s="3" t="n">
-        <v>8375.860000000001</v>
-      </c>
+      <c r="D95" s="3" t="n"/>
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
@@ -17712,9 +17980,7 @@
       <c r="C96" s="3" t="n">
         <v>28328.4</v>
       </c>
-      <c r="D96" s="3" t="n">
-        <v>8365.49</v>
-      </c>
+      <c r="D96" s="3" t="n"/>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
@@ -17739,9 +18005,7 @@
       <c r="C97" s="3" t="n">
         <v>28728.1</v>
       </c>
-      <c r="D97" s="3" t="n">
-        <v>8354.02</v>
-      </c>
+      <c r="D97" s="3" t="n"/>
       <c r="E97" s="3" t="n">
         <v>0</v>
       </c>
@@ -17791,7 +18055,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>现货日前交易价格曲线</t>
+          <t>现货实时交易价格曲线</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -17804,20 +18068,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>实际系统负荷</t>
+          <t>现货日前交易价格曲线</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新能源实际发电曲线</t>
+          <t>实际系统负荷</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -17830,7 +18094,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>日前非市场化机组总出力</t>
+          <t>新能源实际发电曲线</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -17843,7 +18107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>省间联络线输电情况</t>
+          <t>发电总出力</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -17856,24 +18120,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>各时段各类电源电量</t>
+          <t>省间联络线输电情况</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>960</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>各时段各类电源电量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>768</v>
+        <v>960</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -17882,30 +18146,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>实时储能充电计划及电价</t>
+          <t>各时段各类电源的开机台数</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>768</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>日前储能充电计划及电价</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>96</v>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>日前储能充电计划及电价</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/review-results/复盘信息抓取-20260901.xlsx
+++ b/review-results/复盘信息抓取-20260901.xlsx
@@ -15630,7 +15630,9 @@
       <c r="C2" s="3" t="n">
         <v>28733.9</v>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="3" t="n">
+        <v>8469.790000000001</v>
+      </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
@@ -15655,7 +15657,9 @@
       <c r="C3" s="3" t="n">
         <v>28657.3</v>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="n">
+        <v>8460.120000000001</v>
+      </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
@@ -15680,7 +15684,9 @@
       <c r="C4" s="3" t="n">
         <v>28454.4</v>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>8449.43</v>
+      </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
@@ -15705,7 +15711,9 @@
       <c r="C5" s="3" t="n">
         <v>28386</v>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>8440.84</v>
+      </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
@@ -15730,7 +15738,9 @@
       <c r="C6" s="3" t="n">
         <v>29340.5</v>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>8426.799999999999</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
@@ -15755,7 +15765,9 @@
       <c r="C7" s="3" t="n">
         <v>29041.5</v>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="3" t="n">
+        <v>8419.35</v>
+      </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
@@ -15780,7 +15792,9 @@
       <c r="C8" s="3" t="n">
         <v>28975.6</v>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="n">
+        <v>8413.73</v>
+      </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
@@ -15805,7 +15819,9 @@
       <c r="C9" s="3" t="n">
         <v>28575.7</v>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="3" t="n">
+        <v>8406.17</v>
+      </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
@@ -15830,7 +15846,9 @@
       <c r="C10" s="3" t="n">
         <v>30675.2</v>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>8398.01</v>
+      </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
@@ -15855,7 +15873,9 @@
       <c r="C11" s="3" t="n">
         <v>30603.5</v>
       </c>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>8391.42</v>
+      </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
@@ -15880,7 +15900,9 @@
       <c r="C12" s="3" t="n">
         <v>29623.7</v>
       </c>
-      <c r="D12" s="3" t="n"/>
+      <c r="D12" s="3" t="n">
+        <v>8385.280000000001</v>
+      </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
@@ -15905,7 +15927,9 @@
       <c r="C13" s="3" t="n">
         <v>29597.5</v>
       </c>
-      <c r="D13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>8378.5</v>
+      </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
@@ -15930,7 +15954,9 @@
       <c r="C14" s="3" t="n">
         <v>28805.1</v>
       </c>
-      <c r="D14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
+        <v>8375.540000000001</v>
+      </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
@@ -15955,7 +15981,9 @@
       <c r="C15" s="3" t="n">
         <v>28541</v>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>8369.610000000001</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
@@ -15980,7 +16008,9 @@
       <c r="C16" s="3" t="n">
         <v>28403.3</v>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>8364.540000000001</v>
+      </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
@@ -16005,7 +16035,9 @@
       <c r="C17" s="3" t="n">
         <v>27788.1</v>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="3" t="n">
+        <v>8359.049999999999</v>
+      </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
@@ -16030,7 +16062,9 @@
       <c r="C18" s="3" t="n">
         <v>28123.9</v>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
+        <v>8365.549999999999</v>
+      </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
@@ -16055,7 +16089,9 @@
       <c r="C19" s="3" t="n">
         <v>27779.9</v>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
+        <v>8363.299999999999</v>
+      </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
@@ -16080,7 +16116,9 @@
       <c r="C20" s="3" t="n">
         <v>27846.3</v>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>8361.969999999999</v>
+      </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
@@ -16105,7 +16143,9 @@
       <c r="C21" s="3" t="n">
         <v>27881.6</v>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
+        <v>8357.209999999999</v>
+      </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
@@ -16130,7 +16170,9 @@
       <c r="C22" s="3" t="n">
         <v>28190.5</v>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
+        <v>8357.01</v>
+      </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
@@ -16155,7 +16197,9 @@
       <c r="C23" s="3" t="n">
         <v>28339.2</v>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>8358.02</v>
+      </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
@@ -16180,7 +16224,9 @@
       <c r="C24" s="3" t="n">
         <v>28465.3</v>
       </c>
-      <c r="D24" s="3" t="n"/>
+      <c r="D24" s="3" t="n">
+        <v>8365.299999999999</v>
+      </c>
       <c r="E24" s="3" t="n">
         <v>7</v>
       </c>
@@ -16205,7 +16251,9 @@
       <c r="C25" s="3" t="n">
         <v>28793.8</v>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>8367.16</v>
+      </c>
       <c r="E25" s="3" t="n">
         <v>89.09999999999999</v>
       </c>
@@ -16230,7 +16278,9 @@
       <c r="C26" s="3" t="n">
         <v>29071.7</v>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
+        <v>8143.12</v>
+      </c>
       <c r="E26" s="3" t="n">
         <v>356.4</v>
       </c>
@@ -16255,7 +16305,9 @@
       <c r="C27" s="3" t="n">
         <v>29252.3</v>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>7709.08</v>
+      </c>
       <c r="E27" s="3" t="n">
         <v>759.1</v>
       </c>
@@ -16280,7 +16332,9 @@
       <c r="C28" s="3" t="n">
         <v>28805.5</v>
       </c>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>7025.75</v>
+      </c>
       <c r="E28" s="3" t="n">
         <v>1325.4</v>
       </c>
@@ -16305,7 +16359,9 @@
       <c r="C29" s="3" t="n">
         <v>27816.2</v>
       </c>
-      <c r="D29" s="3" t="n"/>
+      <c r="D29" s="3" t="n">
+        <v>6351.08</v>
+      </c>
       <c r="E29" s="3" t="n">
         <v>2017.2</v>
       </c>
@@ -16330,7 +16386,9 @@
       <c r="C30" s="3" t="n">
         <v>27817.5</v>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>5887.63</v>
+      </c>
       <c r="E30" s="3" t="n">
         <v>2801.2</v>
       </c>
@@ -16355,7 +16413,9 @@
       <c r="C31" s="3" t="n">
         <v>26936.8</v>
       </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>5406.66</v>
+      </c>
       <c r="E31" s="3" t="n">
         <v>3694.8</v>
       </c>
@@ -16380,7 +16440,9 @@
       <c r="C32" s="3" t="n">
         <v>26372.2</v>
       </c>
-      <c r="D32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
+        <v>4946.22</v>
+      </c>
       <c r="E32" s="3" t="n">
         <v>4574.6</v>
       </c>
@@ -16405,7 +16467,9 @@
       <c r="C33" s="3" t="n">
         <v>26151.5</v>
       </c>
-      <c r="D33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>4531.53</v>
+      </c>
       <c r="E33" s="3" t="n">
         <v>5624.1</v>
       </c>
@@ -16430,7 +16494,9 @@
       <c r="C34" s="3" t="n">
         <v>26160.2</v>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
+        <v>4184.9</v>
+      </c>
       <c r="E34" s="3" t="n">
         <v>6601.1</v>
       </c>
@@ -16455,7 +16521,9 @@
       <c r="C35" s="3" t="n">
         <v>26242.9</v>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
+        <v>4131.34</v>
+      </c>
       <c r="E35" s="3" t="n">
         <v>7442.1</v>
       </c>
@@ -16480,7 +16548,9 @@
       <c r="C36" s="3" t="n">
         <v>25697.8</v>
       </c>
-      <c r="D36" s="3" t="n"/>
+      <c r="D36" s="3" t="n">
+        <v>4165.76</v>
+      </c>
       <c r="E36" s="3" t="n">
         <v>8148.2</v>
       </c>
@@ -16505,7 +16575,9 @@
       <c r="C37" s="3" t="n">
         <v>25462.6</v>
       </c>
-      <c r="D37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>4177.73</v>
+      </c>
       <c r="E37" s="3" t="n">
         <v>8710.5</v>
       </c>
@@ -16530,7 +16602,9 @@
       <c r="C38" s="3" t="n">
         <v>25112.7</v>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="3" t="n">
+        <v>4202.95</v>
+      </c>
       <c r="E38" s="3" t="n">
         <v>9337.700000000001</v>
       </c>
@@ -16555,7 +16629,9 @@
       <c r="C39" s="3" t="n">
         <v>24681.6</v>
       </c>
-      <c r="D39" s="3" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>4234.98</v>
+      </c>
       <c r="E39" s="3" t="n">
         <v>9769.299999999999</v>
       </c>
@@ -16580,7 +16656,9 @@
       <c r="C40" s="3" t="n">
         <v>24691.5</v>
       </c>
-      <c r="D40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>4276.17</v>
+      </c>
       <c r="E40" s="3" t="n">
         <v>9695.799999999999</v>
       </c>
@@ -16605,7 +16683,9 @@
       <c r="C41" s="3" t="n">
         <v>24250</v>
       </c>
-      <c r="D41" s="3" t="n"/>
+      <c r="D41" s="3" t="n">
+        <v>4290.27</v>
+      </c>
       <c r="E41" s="3" t="n">
         <v>9266.9</v>
       </c>
@@ -16630,7 +16710,9 @@
       <c r="C42" s="3" t="n">
         <v>24420.1</v>
       </c>
-      <c r="D42" s="3" t="n"/>
+      <c r="D42" s="3" t="n">
+        <v>4314.45</v>
+      </c>
       <c r="E42" s="3" t="n">
         <v>9417.1</v>
       </c>
@@ -16655,7 +16737,9 @@
       <c r="C43" s="3" t="n">
         <v>24473.7</v>
       </c>
-      <c r="D43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
+        <v>4331.38</v>
+      </c>
       <c r="E43" s="3" t="n">
         <v>9414.799999999999</v>
       </c>
@@ -16680,7 +16764,9 @@
       <c r="C44" s="3" t="n">
         <v>24508.9</v>
       </c>
-      <c r="D44" s="3" t="n"/>
+      <c r="D44" s="3" t="n">
+        <v>4357.8</v>
+      </c>
       <c r="E44" s="3" t="n">
         <v>9667.200000000001</v>
       </c>
@@ -16705,7 +16791,9 @@
       <c r="C45" s="3" t="n">
         <v>24564</v>
       </c>
-      <c r="D45" s="3" t="n"/>
+      <c r="D45" s="3" t="n">
+        <v>4366.63</v>
+      </c>
       <c r="E45" s="3" t="n">
         <v>9996.799999999999</v>
       </c>
@@ -16730,7 +16818,9 @@
       <c r="C46" s="3" t="n">
         <v>26246.1</v>
       </c>
-      <c r="D46" s="3" t="n"/>
+      <c r="D46" s="3" t="n">
+        <v>4395.82</v>
+      </c>
       <c r="E46" s="3" t="n">
         <v>11289</v>
       </c>
@@ -16755,7 +16845,9 @@
       <c r="C47" s="3" t="n">
         <v>26175.9</v>
       </c>
-      <c r="D47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>4415.28</v>
+      </c>
       <c r="E47" s="3" t="n">
         <v>11699</v>
       </c>
@@ -16780,7 +16872,9 @@
       <c r="C48" s="3" t="n">
         <v>25690</v>
       </c>
-      <c r="D48" s="3" t="n"/>
+      <c r="D48" s="3" t="n">
+        <v>4412.62</v>
+      </c>
       <c r="E48" s="3" t="n">
         <v>11537.9</v>
       </c>
@@ -16805,7 +16899,9 @@
       <c r="C49" s="3" t="n">
         <v>24471.3</v>
       </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>4366.12</v>
+      </c>
       <c r="E49" s="3" t="n">
         <v>11331.1</v>
       </c>
@@ -16830,7 +16926,9 @@
       <c r="C50" s="3" t="n">
         <v>24840.2</v>
       </c>
-      <c r="D50" s="3" t="n"/>
+      <c r="D50" s="3" t="n">
+        <v>4371.46</v>
+      </c>
       <c r="E50" s="3" t="n">
         <v>11673.4</v>
       </c>
@@ -16855,7 +16953,9 @@
       <c r="C51" s="3" t="n">
         <v>24879.7</v>
       </c>
-      <c r="D51" s="3" t="n"/>
+      <c r="D51" s="3" t="n">
+        <v>4352.78</v>
+      </c>
       <c r="E51" s="3" t="n">
         <v>11656.4</v>
       </c>
@@ -16880,7 +16980,9 @@
       <c r="C52" s="3" t="n">
         <v>24570.9</v>
       </c>
-      <c r="D52" s="3" t="n"/>
+      <c r="D52" s="3" t="n">
+        <v>4368.49</v>
+      </c>
       <c r="E52" s="3" t="n">
         <v>11529.7</v>
       </c>
@@ -16905,7 +17007,9 @@
       <c r="C53" s="3" t="n">
         <v>24892.6</v>
       </c>
-      <c r="D53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>4367.9</v>
+      </c>
       <c r="E53" s="3" t="n">
         <v>11555.1</v>
       </c>
@@ -16930,7 +17034,9 @@
       <c r="C54" s="3" t="n">
         <v>25109.4</v>
       </c>
-      <c r="D54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>4358.7</v>
+      </c>
       <c r="E54" s="3" t="n">
         <v>11394.5</v>
       </c>
@@ -16955,7 +17061,9 @@
       <c r="C55" s="3" t="n">
         <v>25250.3</v>
       </c>
-      <c r="D55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>4359.53</v>
+      </c>
       <c r="E55" s="3" t="n">
         <v>11434.4</v>
       </c>
@@ -16980,7 +17088,9 @@
       <c r="C56" s="3" t="n">
         <v>25482.2</v>
       </c>
-      <c r="D56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>4355.94</v>
+      </c>
       <c r="E56" s="3" t="n">
         <v>11208.7</v>
       </c>
@@ -17005,7 +17115,9 @@
       <c r="C57" s="3" t="n">
         <v>25398.3</v>
       </c>
-      <c r="D57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>4347.6</v>
+      </c>
       <c r="E57" s="3" t="n">
         <v>10812</v>
       </c>
@@ -17030,7 +17142,9 @@
       <c r="C58" s="3" t="n">
         <v>26034.9</v>
       </c>
-      <c r="D58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>4334.79</v>
+      </c>
       <c r="E58" s="3" t="n">
         <v>10482.5</v>
       </c>
@@ -17055,7 +17169,9 @@
       <c r="C59" s="3" t="n">
         <v>26256.7</v>
       </c>
-      <c r="D59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>4351.18</v>
+      </c>
       <c r="E59" s="3" t="n">
         <v>9945.200000000001</v>
       </c>
@@ -17080,7 +17196,9 @@
       <c r="C60" s="3" t="n">
         <v>26676.4</v>
       </c>
-      <c r="D60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>4345.68</v>
+      </c>
       <c r="E60" s="3" t="n">
         <v>9774.700000000001</v>
       </c>
@@ -17105,7 +17223,9 @@
       <c r="C61" s="3" t="n">
         <v>26870.1</v>
       </c>
-      <c r="D61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>4322.28</v>
+      </c>
       <c r="E61" s="3" t="n">
         <v>9439.700000000001</v>
       </c>
@@ -17130,7 +17250,9 @@
       <c r="C62" s="3" t="n">
         <v>27201.4</v>
       </c>
-      <c r="D62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>4401.33</v>
+      </c>
       <c r="E62" s="3" t="n">
         <v>8903.5</v>
       </c>
@@ -17155,7 +17277,9 @@
       <c r="C63" s="3" t="n">
         <v>28113.2</v>
       </c>
-      <c r="D63" s="3" t="n"/>
+      <c r="D63" s="3" t="n">
+        <v>4782.72</v>
+      </c>
       <c r="E63" s="3" t="n">
         <v>8444.299999999999</v>
       </c>
@@ -17180,7 +17304,9 @@
       <c r="C64" s="3" t="n">
         <v>28504.6</v>
       </c>
-      <c r="D64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>5207.14</v>
+      </c>
       <c r="E64" s="3" t="n">
         <v>7969.9</v>
       </c>
@@ -17205,7 +17331,9 @@
       <c r="C65" s="3" t="n">
         <v>28968.9</v>
       </c>
-      <c r="D65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>5878.63</v>
+      </c>
       <c r="E65" s="3" t="n">
         <v>7210.5</v>
       </c>
@@ -17230,7 +17358,9 @@
       <c r="C66" s="3" t="n">
         <v>29785.8</v>
       </c>
-      <c r="D66" s="3" t="n"/>
+      <c r="D66" s="3" t="n">
+        <v>6546.52</v>
+      </c>
       <c r="E66" s="3" t="n">
         <v>6478.7</v>
       </c>
@@ -17255,7 +17385,9 @@
       <c r="C67" s="3" t="n">
         <v>30720.8</v>
       </c>
-      <c r="D67" s="3" t="n"/>
+      <c r="D67" s="3" t="n">
+        <v>7010.45</v>
+      </c>
       <c r="E67" s="3" t="n">
         <v>5780.7</v>
       </c>
@@ -17280,7 +17412,9 @@
       <c r="C68" s="3" t="n">
         <v>31812.4</v>
       </c>
-      <c r="D68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>7476.59</v>
+      </c>
       <c r="E68" s="3" t="n">
         <v>4917.5</v>
       </c>
@@ -17305,7 +17439,9 @@
       <c r="C69" s="3" t="n">
         <v>33027.1</v>
       </c>
-      <c r="D69" s="3" t="n"/>
+      <c r="D69" s="3" t="n">
+        <v>7938.2</v>
+      </c>
       <c r="E69" s="3" t="n">
         <v>4066.9</v>
       </c>
@@ -17330,7 +17466,9 @@
       <c r="C70" s="3" t="n">
         <v>34254.8</v>
       </c>
-      <c r="D70" s="3" t="n"/>
+      <c r="D70" s="3" t="n">
+        <v>8352.440000000001</v>
+      </c>
       <c r="E70" s="3" t="n">
         <v>3167.9</v>
       </c>
@@ -17355,7 +17493,9 @@
       <c r="C71" s="3" t="n">
         <v>34931.5</v>
       </c>
-      <c r="D71" s="3" t="n"/>
+      <c r="D71" s="3" t="n">
+        <v>8562.01</v>
+      </c>
       <c r="E71" s="3" t="n">
         <v>2286.4</v>
       </c>
@@ -17380,7 +17520,9 @@
       <c r="C72" s="3" t="n">
         <v>35486.6</v>
       </c>
-      <c r="D72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>8529.58</v>
+      </c>
       <c r="E72" s="3" t="n">
         <v>1530.6</v>
       </c>
@@ -17405,7 +17547,9 @@
       <c r="C73" s="3" t="n">
         <v>36088.2</v>
       </c>
-      <c r="D73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>8502.059999999999</v>
+      </c>
       <c r="E73" s="3" t="n">
         <v>934.5</v>
       </c>
@@ -17430,7 +17574,9 @@
       <c r="C74" s="3" t="n">
         <v>35760.2</v>
       </c>
-      <c r="D74" s="3" t="n"/>
+      <c r="D74" s="3" t="n">
+        <v>8486.290000000001</v>
+      </c>
       <c r="E74" s="3" t="n">
         <v>497.2</v>
       </c>
@@ -17455,7 +17601,9 @@
       <c r="C75" s="3" t="n">
         <v>36061.8</v>
       </c>
-      <c r="D75" s="3" t="n"/>
+      <c r="D75" s="3" t="n">
+        <v>8473.309999999999</v>
+      </c>
       <c r="E75" s="3" t="n">
         <v>190.4</v>
       </c>
@@ -17480,7 +17628,9 @@
       <c r="C76" s="3" t="n">
         <v>36125.6</v>
       </c>
-      <c r="D76" s="3" t="n"/>
+      <c r="D76" s="3" t="n">
+        <v>8470.440000000001</v>
+      </c>
       <c r="E76" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -17505,7 +17655,9 @@
       <c r="C77" s="3" t="n">
         <v>36064.3</v>
       </c>
-      <c r="D77" s="3" t="n"/>
+      <c r="D77" s="3" t="n">
+        <v>8466.120000000001</v>
+      </c>
       <c r="E77" s="3" t="n">
         <v>0</v>
       </c>
@@ -17530,7 +17682,9 @@
       <c r="C78" s="3" t="n">
         <v>36030.9</v>
       </c>
-      <c r="D78" s="3" t="n"/>
+      <c r="D78" s="3" t="n">
+        <v>8467.18</v>
+      </c>
       <c r="E78" s="3" t="n">
         <v>0</v>
       </c>
@@ -17555,7 +17709,9 @@
       <c r="C79" s="3" t="n">
         <v>35727.2</v>
       </c>
-      <c r="D79" s="3" t="n"/>
+      <c r="D79" s="3" t="n">
+        <v>8475.75</v>
+      </c>
       <c r="E79" s="3" t="n">
         <v>0</v>
       </c>
@@ -17580,7 +17736,9 @@
       <c r="C80" s="3" t="n">
         <v>35227.6</v>
       </c>
-      <c r="D80" s="3" t="n"/>
+      <c r="D80" s="3" t="n">
+        <v>8484.969999999999</v>
+      </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
@@ -17605,7 +17763,9 @@
       <c r="C81" s="3" t="n">
         <v>34536.7</v>
       </c>
-      <c r="D81" s="3" t="n"/>
+      <c r="D81" s="3" t="n">
+        <v>8492.42</v>
+      </c>
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
@@ -17630,7 +17790,9 @@
       <c r="C82" s="3" t="n">
         <v>34543.9</v>
       </c>
-      <c r="D82" s="3" t="n"/>
+      <c r="D82" s="3" t="n">
+        <v>8494.379999999999</v>
+      </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
@@ -17655,7 +17817,9 @@
       <c r="C83" s="3" t="n">
         <v>34088.9</v>
       </c>
-      <c r="D83" s="3" t="n"/>
+      <c r="D83" s="3" t="n">
+        <v>8496.360000000001</v>
+      </c>
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
@@ -17680,7 +17844,9 @@
       <c r="C84" s="3" t="n">
         <v>33923.7</v>
       </c>
-      <c r="D84" s="3" t="n"/>
+      <c r="D84" s="3" t="n">
+        <v>8495.709999999999</v>
+      </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
@@ -17705,7 +17871,9 @@
       <c r="C85" s="3" t="n">
         <v>33451.3</v>
       </c>
-      <c r="D85" s="3" t="n"/>
+      <c r="D85" s="3" t="n">
+        <v>8496.389999999999</v>
+      </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
@@ -17730,7 +17898,9 @@
       <c r="C86" s="3" t="n">
         <v>33342.4</v>
       </c>
-      <c r="D86" s="3" t="n"/>
+      <c r="D86" s="3" t="n">
+        <v>8477.68</v>
+      </c>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
@@ -17755,7 +17925,9 @@
       <c r="C87" s="3" t="n">
         <v>32902.6</v>
       </c>
-      <c r="D87" s="3" t="n"/>
+      <c r="D87" s="3" t="n">
+        <v>8474.290000000001</v>
+      </c>
       <c r="E87" s="3" t="n">
         <v>0</v>
       </c>
@@ -17780,7 +17952,9 @@
       <c r="C88" s="3" t="n">
         <v>32520</v>
       </c>
-      <c r="D88" s="3" t="n"/>
+      <c r="D88" s="3" t="n">
+        <v>8471.379999999999</v>
+      </c>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
@@ -17805,7 +17979,9 @@
       <c r="C89" s="3" t="n">
         <v>32117.7</v>
       </c>
-      <c r="D89" s="3" t="n"/>
+      <c r="D89" s="3" t="n">
+        <v>8469.459999999999</v>
+      </c>
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
@@ -17830,7 +18006,9 @@
       <c r="C90" s="3" t="n">
         <v>31796.7</v>
       </c>
-      <c r="D90" s="3" t="n"/>
+      <c r="D90" s="3" t="n">
+        <v>8414.59</v>
+      </c>
       <c r="E90" s="3" t="n">
         <v>0</v>
       </c>
@@ -17855,7 +18033,9 @@
       <c r="C91" s="3" t="n">
         <v>31317.1</v>
       </c>
-      <c r="D91" s="3" t="n"/>
+      <c r="D91" s="3" t="n">
+        <v>8405.870000000001</v>
+      </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
@@ -17880,7 +18060,9 @@
       <c r="C92" s="3" t="n">
         <v>30612.5</v>
       </c>
-      <c r="D92" s="3" t="n"/>
+      <c r="D92" s="3" t="n">
+        <v>8400.52</v>
+      </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
@@ -17905,7 +18087,9 @@
       <c r="C93" s="3" t="n">
         <v>30284.8</v>
       </c>
-      <c r="D93" s="3" t="n"/>
+      <c r="D93" s="3" t="n">
+        <v>8393.719999999999</v>
+      </c>
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
@@ -17930,7 +18114,9 @@
       <c r="C94" s="3" t="n">
         <v>29722.3</v>
       </c>
-      <c r="D94" s="3" t="n"/>
+      <c r="D94" s="3" t="n">
+        <v>8386.32</v>
+      </c>
       <c r="E94" s="3" t="n">
         <v>0</v>
       </c>
@@ -17955,7 +18141,9 @@
       <c r="C95" s="3" t="n">
         <v>29172.8</v>
       </c>
-      <c r="D95" s="3" t="n"/>
+      <c r="D95" s="3" t="n">
+        <v>8375.860000000001</v>
+      </c>
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
@@ -17980,7 +18168,9 @@
       <c r="C96" s="3" t="n">
         <v>28328.4</v>
       </c>
-      <c r="D96" s="3" t="n"/>
+      <c r="D96" s="3" t="n">
+        <v>8365.49</v>
+      </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
@@ -18005,7 +18195,9 @@
       <c r="C97" s="3" t="n">
         <v>28728.1</v>
       </c>
-      <c r="D97" s="3" t="n"/>
+      <c r="D97" s="3" t="n">
+        <v>8354.02</v>
+      </c>
       <c r="E97" s="3" t="n">
         <v>0</v>
       </c>
@@ -18159,26 +18351,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>实时储能充电计划及电价</t>
+          <t>日前非市场化机组总出力</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>日前储能充电计划及电价</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>96</v>
       </c>
       <c r="C11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>日前储能充电计划及电价</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>96</v>
+      </c>
+      <c r="C12" t="n">
         <v>9</v>
       </c>
     </row>
